--- a/iFST_online_PsychoPy/messages.xlsx
+++ b/iFST_online_PsychoPy/messages.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uclouvain-my.sharepoint.com/personal/marcos_morenoverdu_uclouvain_be/Documents/BAS-Lab/Github repositories/iFST/iFST_local_PsychoPy/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uclouvain-my.sharepoint.com/personal/marcos_morenoverdu_uclouvain_be/Documents/BAS-Lab/Github repositories/iFST/iFST_online_PsychoPy/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="489" documentId="8_{439F560A-EC9A-4A85-BCCA-B610A865D2B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0A7ACB62-C721-4533-A069-09ADE2C17C78}"/>
+  <xr:revisionPtr revIDLastSave="494" documentId="8_{439F560A-EC9A-4A85-BCCA-B610A865D2B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4F8AF47F-F0FA-4105-9509-59B9D2B80856}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -96,7 +96,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="223">
   <si>
     <t>EN</t>
   </si>
@@ -258,14 +258,6 @@
     <t>Trial completado</t>
   </si>
   <si>
-    <t>Imagined Finger Sequence Task
-(iFST)</t>
-  </si>
-  <si>
-    <t>Tarea de Secuencia de Dedos Imaginada
-(TSDi)</t>
-  </si>
-  <si>
     <t>block_end_msg</t>
   </si>
   <si>
@@ -549,10 +541,6 @@
 L'objectif de cette tâche est d'évaluer votre capacité à imaginer les mouvements des doigts.</t>
   </si>
   <si>
-    <t>Tâche de séquence de doigts imaginée
-(TSDi)</t>
-  </si>
-  <si>
     <t>segundos</t>
   </si>
   <si>
@@ -620,10 +608,6 @@
   </si>
   <si>
     <t>Weiter</t>
-  </si>
-  <si>
-    <t>Vorgestellte Fingersequenzaufgabe
-(iFST)</t>
   </si>
   <si>
     <t>Leertaste drücken, um fortzufahren</t>
@@ -845,7 +829,16 @@
     <t>right_msg</t>
   </si>
   <si>
-    <t>Rechte</t>
+    <t>Imagined Finger Sequence Task (iFST)</t>
+  </si>
+  <si>
+    <t>Tarea de Secuencia de Dedos Imaginada (TSDi)</t>
+  </si>
+  <si>
+    <t>Tâche de séquence de doigts imaginée (TSDi)</t>
+  </si>
+  <si>
+    <t>Vorgestellte Fingersequenzaufgabe (iFST)</t>
   </si>
 </sst>
 </file>
@@ -949,6 +942,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1268,24 +1265,24 @@
         <v>10</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>50</v>
+        <v>219</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>51</v>
+        <v>220</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>131</v>
+        <v>221</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>155</v>
+        <v>222</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -1293,16 +1290,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E3" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -1316,10 +1313,10 @@
         <v>5</v>
       </c>
       <c r="D4" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E4" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -1333,10 +1330,10 @@
         <v>9</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -1353,7 +1350,7 @@
         <v>12</v>
       </c>
       <c r="E6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -1370,41 +1367,41 @@
         <v>28</v>
       </c>
       <c r="E7" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
+        <v>76</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C8" t="s">
         <v>78</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="C8" t="s">
-        <v>80</v>
-      </c>
       <c r="D8" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E8" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C9" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D9" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E9" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -1412,16 +1409,16 @@
         <v>22</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -1429,16 +1426,16 @@
         <v>19</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -1446,16 +1443,16 @@
         <v>21</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D12" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="C12" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>124</v>
-      </c>
       <c r="E12" s="4" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -1469,15 +1466,15 @@
         <v>26</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>23</v>
@@ -1486,7 +1483,7 @@
         <v>24</v>
       </c>
       <c r="D14" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>23</v>
@@ -1494,7 +1491,7 @@
     </row>
     <row r="15" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>17</v>
@@ -1503,27 +1500,27 @@
         <v>18</v>
       </c>
       <c r="D15" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
+        <v>50</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C16" t="s">
         <v>52</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C16" t="s">
-        <v>54</v>
-      </c>
       <c r="D16" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -1537,10 +1534,10 @@
         <v>16</v>
       </c>
       <c r="D17" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E17" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -1548,21 +1545,21 @@
         <v>30</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C18" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D18" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E18" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>31</v>
@@ -1571,15 +1568,15 @@
         <v>32</v>
       </c>
       <c r="D19" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>33</v>
@@ -1588,10 +1585,10 @@
         <v>34</v>
       </c>
       <c r="D20" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -1605,10 +1602,10 @@
         <v>37</v>
       </c>
       <c r="D21" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E21" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -1622,10 +1619,10 @@
         <v>40</v>
       </c>
       <c r="D22" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E22" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -1639,10 +1636,10 @@
         <v>43</v>
       </c>
       <c r="D23" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E23" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -1656,10 +1653,10 @@
         <v>46</v>
       </c>
       <c r="D24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E24" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -1673,338 +1670,338 @@
         <v>49</v>
       </c>
       <c r="D25" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E25" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C26" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D26" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E26" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C27" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D27" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E27" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C28" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D28" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E28" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C29" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D29" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E29" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
+        <v>61</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C30" t="s">
         <v>63</v>
       </c>
-      <c r="B30" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C30" t="s">
-        <v>65</v>
-      </c>
       <c r="D30" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E30" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C31" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="D31" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="D31" s="5" t="s">
-        <v>100</v>
-      </c>
       <c r="E31" s="4" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C32" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="D32" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="D32" s="4" t="s">
-        <v>101</v>
-      </c>
       <c r="E32" s="4" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
+        <v>89</v>
+      </c>
+      <c r="B33" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>93</v>
-      </c>
       <c r="C33" s="5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
+        <v>162</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="C35" t="s">
+        <v>164</v>
+      </c>
+      <c r="D35" t="s">
+        <v>165</v>
+      </c>
+      <c r="E35" t="s">
         <v>166</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="C35" t="s">
-        <v>168</v>
-      </c>
-      <c r="D35" t="s">
-        <v>169</v>
-      </c>
-      <c r="E35" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
+        <v>167</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="C36" t="s">
+        <v>169</v>
+      </c>
+      <c r="D36" t="s">
+        <v>170</v>
+      </c>
+      <c r="E36" t="s">
         <v>171</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="C36" t="s">
-        <v>173</v>
-      </c>
-      <c r="D36" t="s">
-        <v>174</v>
-      </c>
-      <c r="E36" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
+        <v>172</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C37" t="s">
+        <v>174</v>
+      </c>
+      <c r="D37" t="s">
+        <v>175</v>
+      </c>
+      <c r="E37" t="s">
         <v>176</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="C37" t="s">
-        <v>178</v>
-      </c>
-      <c r="D37" t="s">
-        <v>179</v>
-      </c>
-      <c r="E37" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
+        <v>177</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C38" t="s">
+        <v>179</v>
+      </c>
+      <c r="D38" t="s">
+        <v>180</v>
+      </c>
+      <c r="E38" t="s">
         <v>181</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="C38" t="s">
-        <v>183</v>
-      </c>
-      <c r="D38" t="s">
-        <v>184</v>
-      </c>
-      <c r="E38" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
+        <v>182</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C39" t="s">
+        <v>184</v>
+      </c>
+      <c r="D39" t="s">
+        <v>185</v>
+      </c>
+      <c r="E39" t="s">
         <v>186</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="C39" t="s">
-        <v>188</v>
-      </c>
-      <c r="D39" t="s">
-        <v>189</v>
-      </c>
-      <c r="E39" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
+        <v>187</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="C40" t="s">
+        <v>189</v>
+      </c>
+      <c r="D40" t="s">
+        <v>190</v>
+      </c>
+      <c r="E40" t="s">
         <v>191</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="C40" t="s">
-        <v>193</v>
-      </c>
-      <c r="D40" t="s">
-        <v>194</v>
-      </c>
-      <c r="E40" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
+        <v>192</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="C41" t="s">
+        <v>194</v>
+      </c>
+      <c r="D41" t="s">
+        <v>195</v>
+      </c>
+      <c r="E41" t="s">
         <v>196</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="C41" t="s">
-        <v>198</v>
-      </c>
-      <c r="D41" t="s">
-        <v>199</v>
-      </c>
-      <c r="E41" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
+        <v>197</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="C42" t="s">
+        <v>199</v>
+      </c>
+      <c r="D42" t="s">
+        <v>200</v>
+      </c>
+      <c r="E42" t="s">
         <v>201</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="C42" t="s">
-        <v>203</v>
-      </c>
-      <c r="D42" t="s">
-        <v>204</v>
-      </c>
-      <c r="E42" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
+        <v>202</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C43" t="s">
+        <v>204</v>
+      </c>
+      <c r="D43" t="s">
+        <v>205</v>
+      </c>
+      <c r="E43" t="s">
         <v>206</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="C43" t="s">
-        <v>208</v>
-      </c>
-      <c r="D43" t="s">
-        <v>209</v>
-      </c>
-      <c r="E43" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
+        <v>207</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="C44" t="s">
+        <v>209</v>
+      </c>
+      <c r="D44" t="s">
+        <v>210</v>
+      </c>
+      <c r="E44" t="s">
         <v>211</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="C44" t="s">
-        <v>213</v>
-      </c>
-      <c r="D44" t="s">
-        <v>214</v>
-      </c>
-      <c r="E44" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>31</v>
@@ -2013,32 +2010,32 @@
         <v>32</v>
       </c>
       <c r="D45" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E45" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
+        <v>213</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C46" t="s">
+        <v>215</v>
+      </c>
+      <c r="D46" t="s">
+        <v>216</v>
+      </c>
+      <c r="E46" t="s">
         <v>217</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="C46" t="s">
-        <v>219</v>
-      </c>
-      <c r="D46" t="s">
-        <v>220</v>
-      </c>
-      <c r="E46" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>33</v>
@@ -2047,27 +2044,27 @@
         <v>34</v>
       </c>
       <c r="D47" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E47" t="s">
-        <v>223</v>
+        <v>141</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
+        <v>61</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C48" t="s">
         <v>63</v>
       </c>
-      <c r="B48" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C48" t="s">
-        <v>65</v>
-      </c>
       <c r="D48" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E48" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -2197,18 +2194,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2228,6 +2225,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3744155D-8FAB-4E67-B5E0-C7FDBFB3715D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3725960-8A89-4E70-9C40-340E0EDB6403}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
@@ -2240,12 +2245,4 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3744155D-8FAB-4E67-B5E0-C7FDBFB3715D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>